--- a/src/make_dummy_data/登録学生一覧.xlsx
+++ b/src/make_dummy_data/登録学生一覧.xlsx
@@ -425,954 +425,2139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>共通ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>学籍番号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>学生氏名</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ごしゅみ</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>もくひょー</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>97993510</t>
+          <t>9279013134</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>こーるど ぷれりん</t>
+          <t>98005222</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>なただり りんぴょ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>書店で背表紙を読む</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>91159695</t>
+          <t>6169182974</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>にゅとーん いさりん</t>
+          <t>94681791</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>まーく らふりん</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>自販機のラインナップ分析</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>レポートを提出期限より前に出す経験をする</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>90651734</t>
+          <t>3343708628</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ふぇでら ろじゃりん</t>
+          <t>90954705</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>けいと うぃんり</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>レシートの長さランキング</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>深夜のネットサーフィンを控える（理想）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>91512015</t>
+          <t>0175301378</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ながさま まさみん</t>
+          <t>91820250</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>にしじま ひでとん</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>消しゴムの角を守る</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>95122801</t>
+          <t>9810224915</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>さかぐてぃ けんたろぴ</t>
+          <t>94287215</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>がりれお るんた</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>新しいショートカットキー探し</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>94408956</t>
+          <t>9940799401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>あんどりゅ りんふ</t>
+          <t>98943564</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>にしこり けいたん</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>自販機のラインナップ分析</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>レポートの誤字を減らす</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>98098503</t>
+          <t>4341794494</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>かりすて ふりん</t>
+          <t>96426990</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>でんぜる わしりん</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>雲の形の解釈</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>93021805</t>
+          <t>4141435048</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>めしりお ねるん</t>
+          <t>92283434</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>へんりー かびりん</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ペン回し（成功率30%）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>94011838</t>
+          <t>9130614515</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ひゅー じゃくりん</t>
+          <t>90506589</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>すかーれ っとりん</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Googleマップで遠くの街を散歩</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>講義に出る回数を増やす</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>99072052</t>
+          <t>0127002595</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>える ふぁにんぬ</t>
+          <t>94262459</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>きむたくん たくやん</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>靴ひもを結び直すタイミング研究</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>講義に5分前に着く人になる</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>96123779</t>
+          <t>5001007037</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>まーらー るぴょ</t>
+          <t>96243156</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>よしだ りんちゃ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>天井の模様を眺める</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>研究室の椅子を壊さない</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>90653843</t>
+          <t>0100744423</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>かわぐてぃ はるにゃ</t>
+          <t>94408956</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>あんどりゅ りんふ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>スマホのバッテリー節約術研究</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>レポートの誤字を減らす</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>96716163</t>
+          <t>7612431523</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>りあーな ぴょんぬ</t>
+          <t>97536739</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>さらー りんみゅ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>コンビニの新商品チェック</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>90043817</t>
+          <t>9508708530</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>みうらか ずたん</t>
+          <t>93046823</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>きあぬ りぶりん</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>書店で背表紙を読む</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>91941830</t>
+          <t>6406409299</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>えどしー らんぴ</t>
+          <t>90722785</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>めしりお ぴょりん</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>レシートの長さランキング</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>スマホを見ない時間を一日5分作る</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>99350122</t>
+          <t>0749763142</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ればんど ふすりん</t>
+          <t>96967984</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>うぃる すみりん</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>コンビニの新商品チェック</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>深夜のネットサーフィンを控える（理想）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>90506589</t>
+          <t>9197188560</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>すかーれ っとりん</t>
+          <t>94504507</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>そんふん みんりん</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>雨が降りそうかどうかの体感予測</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>エレベーターを使わず階段を使う日を作る</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>90954705</t>
+          <t>1840146537</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>けいと うぃんり</t>
+          <t>93251533</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>おおさか なみりん</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>机の上の整理（30分だけ）</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>95012302</t>
+          <t>1003835549</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>えまま そんりん</t>
+          <t>99171192</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ろなくり どるん</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>エスカレーターで立ち位置を考える</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>91808853</t>
+          <t>5304988098</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>めんでれ ふぃん</t>
+          <t>95556337</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>えじそと とまち</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>スーパーの値引きタイミング観察</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>90026696</t>
+          <t>5147308611</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>とびー まぐりん</t>
+          <t>94703520</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>えんどう りんみゅ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>家の周りを一周する</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>研究室の椅子を壊さない</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>94288321</t>
+          <t>3286719596</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ひろしぇ すずたん</t>
+          <t>96195615</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>まついひ できゅ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>雨が降りそうかどうかの体感予測</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>スマホを見ない時間を一日5分作る</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>90111320</t>
+          <t>1681905967</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>いけえ りかこぴ</t>
+          <t>94011838</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ひゅー じゃくりん</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>早歩きと普通歩きの境界研究</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>パソコンのバックアップを取る</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>91019367</t>
+          <t>6620058677</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>あいしゅ たいんるん</t>
+          <t>90026696</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>とびー まぐりん</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>冷蔵庫の中を定期巡回する</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>95619961</t>
+          <t>0859912394</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>じぇにふぁ ろれみゅ</t>
+          <t>96503172</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>でぃかぷり おれおん</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>書店で背表紙を読む</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>エレベーターを使わず階段を使う日を作る</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>92833198</t>
+          <t>5691370262</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ろばー とぱりん</t>
+          <t>98098503</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>かりすて ふりん</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>机のガタつき調整</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>講義に5分前に着く人になる</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>96815845</t>
+          <t>3646283907</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>だるびしゅ ゆうにゃ</t>
+          <t>91658723</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>こぺるに くすみゅ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>コンセントの空きを探す</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>99482770</t>
+          <t>1400073713</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>じょだま いけるん</t>
+          <t>95615247</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>じぇし かちゃり</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>カフェの席取り戦略研究</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>発表スライドを前日に完成させる</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>96471453</t>
+          <t>4451523647</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>はりすた いるんぬ</t>
+          <t>96716163</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>りあーな ぴょんぬ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>YouTubeおすすめの深掘り</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>90041840</t>
+          <t>9937157100</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ねいまー るりん</t>
+          <t>92911384</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>とむ ほらりん</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>自販機のラインナップ分析</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>机の上を週に一度は片付ける</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>97526525</t>
+          <t>2871012615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>きゅりまり りんぬ</t>
+          <t>99422693</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>らべるん みゃ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>おにぎりの具ランキング更新</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>レポートを提出期限より前に出す経験をする</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>91945063</t>
+          <t>5992764226</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>だにえる くらりん</t>
+          <t>91773905</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>くぼ りんた</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>スマホのホーム画面整理</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>96075175</t>
+          <t>7013775407</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>たき りんぴ</t>
+          <t>93222012</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ていすう ふとちゃ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>90514484</t>
+          <t>1718614107</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>みりー ぼびりん</t>
+          <t>93964920</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>えりっく さてぃん</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>メールの件名を考えすぎる</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>96011456</t>
+          <t>5205327525</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>むばっぺ きゅりん</t>
+          <t>97821911</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>あらがち ゆいりん</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>コーヒーを冷ましすぎる</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>研究室のドアをノックする勇気を持つ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>98592767</t>
+          <t>9350348454</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>なだる らふぁみゅ</t>
+          <t>93325513</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>おりびあ ころりん</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>消しゴムの角を守る</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>「あとでやる」を減らす</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>91658723</t>
+          <t>5697806189</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>こぺるに くすみゅ</t>
+          <t>97970565</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>はまなべ みなみゅ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>次にやることを考える</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>91142538</t>
+          <t>2728817242</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ありあな ぐらぴょ</t>
+          <t>94602157</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>じぇいく ぎれりん</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>レポートを提出期限より前に出す経験をする</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>98536163</t>
+          <t>6392257439</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>よしだま さたろ</t>
+          <t>94072064</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>あでるる ぴょみ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>スマホのバッテリー節約術研究</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>レポートを提出期限より前に出す経験をする</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>94262459</t>
+          <t>2645754197</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>きむたくん たくやん</t>
+          <t>98574936</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>さんどら ぶるぴ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>新しいショートカットキー探し</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>スマホを見ない時間を一日5分作る</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>90577055</t>
+          <t>2590396233</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>じぇな おてりん</t>
+          <t>91019367</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>あいしゅ たいんるん</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>天井の模様を眺める</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>90496767</t>
+          <t>0215274990</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>めりる すとりゃ</t>
+          <t>96471453</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>はりすた いるんぬ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>カップ麺の待ち時間アレンジ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>92983686</t>
+          <t>9877702520</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>えみりー ぶらりん</t>
+          <t>94933437</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>まーご っとりん</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>カレンダーの祝日配置チェック</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>97970565</t>
+          <t>4821471876</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>はまなべ みなみゅ</t>
+          <t>92698372</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>もーつぁ るとぴ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>机のガタつき調整</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>95615247</t>
+          <t>9478027019</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>じぇし かちゃり</t>
+          <t>90496767</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>めりる すとりゃ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>スーパーの値引きタイミング観察</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>98282607</t>
+          <t>8977460928</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ぶらぴと ぴっとん</t>
+          <t>95012302</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>えまま そんりん</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>電車の発車メロディ研究</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>96195615</t>
+          <t>2751889001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>まついひ できゅ</t>
+          <t>90653843</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>かわぐてぃ はるにゃ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>お菓子のカロリー計算（食べた後）</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>締切という概念と仲良くなる</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>97536739</t>
+          <t>8018780257</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>さらー りんみゅ</t>
+          <t>95768378</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>しょぱん ぴょり</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>近所の猫の行動観察</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>発表スライドを前日に完成させる</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>98496681</t>
+          <t>4357371252</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>はーらん どりん</t>
+          <t>91176779</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>りすとん るみゃ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>書店で背表紙を読む</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>90228827</t>
+          <t>8224520058</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ぶるーの まるりん</t>
+          <t>91549389</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ぺどり りんぴ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>スーパーの値引きタイミング観察</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>深夜のネットサーフィンを控える（理想）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>92698372</t>
+          <t>6480310755</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>もーつぁ るとぴ</t>
+          <t>93746912</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>べん あふりん</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Google検索の予測変換観察</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>92422894</t>
+          <t>6583911310</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>もりなな ぴょん</t>
+          <t>96011456</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>むばっぺ きゅりん</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>スマホのホーム画面整理</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>93046823</t>
+          <t>0301866209</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>きあぬ りぶりん</t>
+          <t>90514484</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>みりー ぼびりん</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ペン回し（成功率30%）</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>95889112</t>
+          <t>5208144369</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>あやせる はるかるん</t>
+          <t>90111320</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>いけえ りかこぴ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>講義に5分前に着く人になる</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>1973756230</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>98154857</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>ほしのげ げんち</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>早歩きと普通歩きの境界研究</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>寝坊の理由を天候以外にする</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>99704475</t>
+          <t>1301590939</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>けいしー ましゅりん</t>
+          <t>99482770</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>じょだま いけるん</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>おにぎりの具ランキング更新</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>講義に5分前に着く人になる</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>96362653</t>
+          <t>9484049424</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>やまじゃき けんとん</t>
+          <t>98282607</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ぶらぴと ぴっとん</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>コンビニコーヒーの濃さ比較</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>研究室のドアをノックする勇気を持つ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>93283594</t>
+          <t>3329879191</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>どびゅっし ゅりん</t>
+          <t>94994556</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>きたぐわ けいこちゃ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>天気予報の答え合わせ</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>研究の進捗を月に一度は作る</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>95848525</t>
+          <t>0892772298</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ふろーれ んすぴ</t>
+          <t>99349852</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>べねでぃ くとりん</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>カップ麺の待ち時間アレンジ</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>締切の前日に焦らない生活を目指す</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>98943564</t>
+          <t>6056625134</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>にしこり けいたん</t>
+          <t>93767436</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ぼるうさ いんたん</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>天井の模様を眺める</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>積読の本を一冊は読む</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>98005222</t>
+          <t>1002495462</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>なただり りんぴょ</t>
+          <t>98916415</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>くりす へむりん</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>電車の吊り広告を全部読む</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>90302590</t>
+          <t>5397912856</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>すだまちゃ まさきゅ</t>
+          <t>99072052</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>える ふぁにんぬ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>スーパーの値引きタイミング観察</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>研究の進捗を月に一度は作る</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>99484036</t>
+          <t>7229972588</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>あん ねはさりん</t>
+          <t>97947365</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ぱすてる るんぴ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>コンビニコーヒーの濃さ比較</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>95809183</t>
+          <t>1318276249</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>たけうてぃ りょうまる</t>
+          <t>97526525</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>きゅりまり りんぬ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>歩道のタイル模様を追う</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>96251330</t>
+          <t>4709001521</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>いにえす たりん</t>
+          <t>91462747</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ふくだん みらきゅ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>レシートの長さランキング</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>研究室のドアをノックする勇気を持つ</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>98407534</t>
+          <t>4149520758</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ろばーと ぱてりん</t>
+          <t>95122801</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>さかぐてぃ けんたろぴ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ペットボトルのラベル研究</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>92283434</t>
+          <t>5989834735</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>へんりー かびりん</t>
+          <t>93283594</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>どびゅっし ゅりん</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>YouTubeおすすめの深掘り</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>90722785</t>
+          <t>5885388060</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>めしりお ぴょりん</t>
+          <t>90302590</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>すだまちゃ まさきゅ</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>雨が降りそうかどうかの体感予測</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>寝坊の理由を天候以外にする</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>92453456</t>
+          <t>1447507810</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>べーとー べんちゃ</t>
+          <t>92422894</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>もりなな ぴょん</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>天井の模様を眺める</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>机の引き出しの化石を整理する</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>90311811</t>
+          <t>1996851040</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>やまだて つとん</t>
+          <t>90919775</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>しょーん めんりん</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>コンビニコーヒーの濃さ比較</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>研究室の椅子を壊さない</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>93633575</t>
+          <t>8272778455</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>おかざき りんぬ</t>
+          <t>95619961</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>じぇにふぁ ろれみゅ</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>書店で背表紙を読む</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>研究室のドアをノックする勇気を持つ</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>91462747</t>
+          <t>3384968416</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ふくだん みらきゅ</t>
+          <t>90041840</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ねいまー るりん</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>雲の形の解釈</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>課題のファイル名をわかりやすくする</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>94287215</t>
+          <t>1694523937</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>がりれお るんた</t>
+          <t>91142538</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ありあな ぐらぴょ</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>スーパーの値引きタイミング観察</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>99915396</t>
+          <t>6461961544</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>わおたに しょうたいむ</t>
+          <t>97993510</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>こーるど ぷれりん</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>エアコンの最適温度探し</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>昼夜逆転を月に一度は直す</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>94933437</t>
+          <t>1993810950</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>まーご っとりん</t>
+          <t>96123779</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>まーらー るぴょ</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>コンビニの新商品チェック</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>パソコンのバックアップを取る</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>90339372</t>
+          <t>4662150869</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>てすらん にこぴょ</t>
+          <t>97706335</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ぶらっど ぴょりん</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>91029201</t>
+          <t>3080831276</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>さかもとは やとりん</t>
+          <t>98536163</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>よしだま さたろ</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>早歩きと普通歩きの境界研究</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>94944026</t>
+          <t>7846193536</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>くりろな うどりん</t>
+          <t>95571403</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ががれで ぃみゅ</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>メールの件名を考えすぎる</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
         </is>
       </c>
     </row>

--- a/src/make_dummy_data/登録学生一覧.xlsx
+++ b/src/make_dummy_data/登録学生一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,152 +458,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9279013134</t>
+          <t>4356302180</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>98005222</t>
+          <t>88289817</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>なただり りんぴょ</t>
+          <t>おおいずみ ひろしぇ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gitでやらかさない</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6169182974</t>
+          <t>4356302180</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94681791</t>
+          <t>90481394</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>まーく らふりん</t>
+          <t>おおいずみ ひろしぇ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>自販機のラインナップ分析</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>レポートを提出期限より前に出す経験をする</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3343708628</t>
+          <t>2201200418</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90954705</t>
+          <t>84952075</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>けいと うぃんり</t>
+          <t>れおなる どりん</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>レシートの長さランキング</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>深夜のネットサーフィンを控える（理想）</t>
+          <t>昼夜逆転を月に一度は直す</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0175301378</t>
+          <t>2201200418</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91820250</t>
+          <t>94310102</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>にしじま ひでとん</t>
+          <t>れおなる どりん</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>消しゴムの角を守る</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>今年こそ朝型人間になる（予定）</t>
+          <t>昼夜逆転を月に一度は直す</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9810224915</t>
+          <t>8434287215</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>94287215</t>
+          <t>86249761</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>がりれお るんた</t>
+          <t>ていらー すうぃりん</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新しいショートカットキー探し</t>
+          <t>自販機のラインナップ分析</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9940799401</t>
+          <t>8434287215</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>98943564</t>
+          <t>90524669</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>にしこり けいたん</t>
+          <t>ていらー すうぃりん</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,272 +613,272 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>レポートの誤字を減らす</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4341794494</t>
+          <t>4079935100</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>96426990</t>
+          <t>88368367</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>でんぜる わしりん</t>
+          <t>ていすう ふとちゃ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>雲の形の解釈</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>友達の課題の進み具合を見て焦らない</t>
+          <t>「あとでやる」を減らす</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4141435048</t>
+          <t>4079935100</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>92283434</t>
+          <t>96486745</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>へんりー かびりん</t>
+          <t>ていすう ふとちゃ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ペン回し（成功率30%）</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>今年こそ朝型人間になる（予定）</t>
+          <t>「あとでやる」を減らす</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9130614515</t>
+          <t>9919968510</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90506589</t>
+          <t>82531180</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>すかーれ っとりん</t>
+          <t>こーるど ぷれりん</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Googleマップで遠くの街を散歩</t>
+          <t>スマホのバッテリー節約術研究</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0127002595</t>
+          <t>9919968510</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>94262459</t>
+          <t>96807885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>きむたくん たくやん</t>
+          <t>こーるど ぷれりん</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>靴ひもを結び直すタイミング研究</t>
+          <t>スマホのバッテリー節約術研究</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>講義に5分前に着く人になる</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5001007037</t>
+          <t>6912396492</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>96243156</t>
+          <t>82337490</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>よしだ りんちゃ</t>
+          <t>さかもとは やとりん</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>天井の模様を眺める</t>
+          <t>ペットボトルのラベル研究</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>研究室の椅子を壊さない</t>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0100744423</t>
+          <t>6912396492</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>94408956</t>
+          <t>94274525</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>あんどりゅ りんふ</t>
+          <t>さかもとは やとりん</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>スマホのバッテリー節約術研究</t>
+          <t>ペットボトルのラベル研究</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>レポートの誤字を減らす</t>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7612431523</t>
+          <t>9510146274</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>97536739</t>
+          <t>88814174</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>さらー りんみゅ</t>
+          <t>やまじゃき けんとん</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>コンビニの新商品チェック</t>
+          <t>電車の発車メロディ研究</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>パスワードを覚えられるものにする</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9508708530</t>
+          <t>9510146274</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>93046823</t>
+          <t>97709106</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>きあぬ りぶりん</t>
+          <t>やまじゃき けんとん</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>電車の発車メロディ研究</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6406409299</t>
+          <t>4033437086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90722785</t>
+          <t>83968796</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>めしりお ぴょりん</t>
+          <t>なただり りんぴょ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>レシートの長さランキング</t>
+          <t>コンビニコーヒーの濃さ比較</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>スマホを見ない時間を一日5分作る</t>
+          <t>深夜のネットサーフィンを控える（理想）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0749763142</t>
+          <t>4033437086</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>96967984</t>
+          <t>93578742</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>うぃる すみりん</t>
+          <t>なただり りんぴょ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>コンビニの新商品チェック</t>
+          <t>コンビニコーヒーの濃さ比較</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,71 +890,71 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9197188560</t>
+          <t>0593019235</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>94504507</t>
+          <t>83286719</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>そんふん みんりん</t>
+          <t>すあれす りんぴょ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>雨が降りそうかどうかの体感予測</t>
+          <t>早歩きと普通歩きの境界研究</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>エレベーターを使わず階段を使う日を作る</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1840146537</t>
+          <t>0593019235</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>93251533</t>
+          <t>91442685</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>おおさか なみりん</t>
+          <t>すあれす りんぴょ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>机の上の整理（30分だけ）</t>
+          <t>早歩きと普通歩きの境界研究</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1003835549</t>
+          <t>3779815485</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>99171192</t>
+          <t>86586801</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ろなくり どるん</t>
+          <t>ひゅー じゃくりん</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -964,1185 +964,1185 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>講義の質問を一度はしてみる</t>
+          <t>講義に出る回数を増やす</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5304988098</t>
+          <t>3779815485</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>95556337</t>
+          <t>91405223</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>えじそと とまち</t>
+          <t>ひゅー じゃくりん</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>スーパーの値引きタイミング観察</t>
+          <t>エスカレーターで立ち位置を考える</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>講義に出る回数を増やす</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5147308611</t>
+          <t>1029201825</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>94703520</t>
+          <t>82431523</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>えんどう りんみゅ</t>
+          <t>くろーす りんぬ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>家の周りを一周する</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>研究室の椅子を壊さない</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3286719596</t>
+          <t>1029201825</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>96195615</t>
+          <t>95944747</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>まついひ できゅ</t>
+          <t>くろーす りんぬ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>雨が降りそうかどうかの体感予測</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>スマホを見ない時間を一日5分作る</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1681905967</t>
+          <t>4259232515</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>94011838</t>
+          <t>86314208</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ひゅー じゃくりん</t>
+          <t>でびっど べかりん</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>早歩きと普通歩きの境界研究</t>
+          <t>家の周りを一周する</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>パソコンのバックアップを取る</t>
+          <t>図書館で寝ない</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6620058677</t>
+          <t>4259232515</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90026696</t>
+          <t>95482699</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>とびー まぐりん</t>
+          <t>でびっど べかりん</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>冷蔵庫の中を定期巡回する</t>
+          <t>家の周りを一周する</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>図書館で寝ない</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0859912394</t>
+          <t>1615918261</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>96503172</t>
+          <t>82752501</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>でぃかぷり おれおん</t>
+          <t>むらかみ むねきゅん</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>自販機のラインナップ分析</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>エレベーターを使わず階段を使う日を作る</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5691370262</t>
+          <t>1615918261</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>98098503</t>
+          <t>93714532</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>かりすて ふりん</t>
+          <t>むらかみ むねきゅん</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>自販機のラインナップ分析</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>講義に5分前に着く人になる</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3646283907</t>
+          <t>3450123020</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>91658723</t>
+          <t>81691829</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>こぺるに くすみゅ</t>
+          <t>もりなな ぴょん</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>コンセントの空きを探す</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>今年こそ朝型人間になる（予定）</t>
+          <t>講義に5分前に着く人になる</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1400073713</t>
+          <t>3450123020</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>95615247</t>
+          <t>92470093</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>じぇし かちゃり</t>
+          <t>もりなな ぴょん</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>カフェの席取り戦略研究</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>発表スライドを前日に完成させる</t>
+          <t>講義に5分前に着く人になる</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4451523647</t>
+          <t>4681791561</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>96716163</t>
+          <t>89687518</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>りあーな ぴょんぬ</t>
+          <t>べんぜま りんる</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YouTubeおすすめの深掘り</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ノートをちゃんと取る（たぶん）</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9937157100</t>
+          <t>4681791561</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>92911384</t>
+          <t>97309791</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>とむ ほらりん</t>
+          <t>べんぜま りんる</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>自販機のラインナップ分析</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>机の上を週に一度は片付ける</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2871012615</t>
+          <t>0338939162</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>99422693</t>
+          <t>84341794</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>らべるん みゃ</t>
+          <t>ががれで ぃみゅ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>レポートを提出期限より前に出す経験をする</t>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5992764226</t>
+          <t>0338939162</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>91773905</t>
+          <t>91831457</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>くぼ りんた</t>
+          <t>ががれで ぃみゅ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>スマホのホーム画面整理</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>パソコンのアップデートを放置しない</t>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7013775407</t>
+          <t>0840753406</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93222012</t>
+          <t>84171861</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ていすう ふとちゃ</t>
+          <t>ありあな ぐらぴょ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wi-Fiが遅いときにまず自分を疑う</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1718614107</t>
+          <t>0840753406</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93964920</t>
+          <t>97199041</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>えりっく さてぃん</t>
+          <t>ありあな ぐらぴょ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>メールの件名を考えすぎる</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5205327525</t>
+          <t>7286362653</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>97821911</t>
+          <t>84988098</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>あらがち ゆいりん</t>
+          <t>どびゅっし ゅりん</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>書店で背表紙を読む</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>研究室のドアをノックする勇気を持つ</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9350348454</t>
+          <t>7286362653</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93325513</t>
+          <t>96049623</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>おりびあ ころりん</t>
+          <t>どびゅっし ゅりん</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>消しゴムの角を守る</t>
+          <t>書店で背表紙を読む</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>「あとでやる」を減らす</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5697806189</t>
+          <t>2785935012</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>97970565</t>
+          <t>81131005</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>はまなべ みなみゅ</t>
+          <t>そんふん みんりん</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>次にやることを考える</t>
+          <t>書店で背表紙を読む</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>USBメモリをなくさない一年にする</t>
+          <t>締切の前日に焦らない生活を目指す</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2728817242</t>
+          <t>2785935012</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>94602157</t>
+          <t>96616215</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>じぇいく ぎれりん</t>
+          <t>そんふん みんりん</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>書店で背表紙を読む</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>レポートを提出期限より前に出す経験をする</t>
+          <t>締切の前日に焦らない生活を目指す</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6392257439</t>
+          <t>9365122801</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>94072064</t>
+          <t>80543919</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>あでるる ぴょみ</t>
+          <t>にしじま ひでとん</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>スマホのバッテリー節約術研究</t>
+          <t>新しいボールペンの試し書き</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>レポートを提出期限より前に出す経験をする</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2645754197</t>
+          <t>9365122801</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>98574936</t>
+          <t>94114987</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>さんどら ぶるぴ</t>
+          <t>にしじま ひでとん</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新しいショートカットキー探し</t>
+          <t>新しいボールペンの試し書き</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>スマホを見ない時間を一日5分作る</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2590396233</t>
+          <t>3774757058</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>91019367</t>
+          <t>87424789</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>あいしゅ たいんるん</t>
+          <t>ぶらぴと ぴっとん</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>天井の模様を眺める</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>パスワードを覚えられるものにする</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0215274990</t>
+          <t>3774757058</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>96471453</t>
+          <t>96988445</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>はりすた いるんぬ</t>
+          <t>ぶらぴと ぴっとん</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>カップ麺の待ち時間アレンジ</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9877702520</t>
+          <t>5660049440</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>94933437</t>
+          <t>88760914</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>まーご っとりん</t>
+          <t>はりすた いるんぬ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>カレンダーの祝日配置チェック</t>
+          <t>早歩きと普通歩きの境界研究</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>パソコンのアップデートを放置しない</t>
+          <t>講義中に眠くならない方法を研究する</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4821471876</t>
+          <t>5660049440</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>92698372</t>
+          <t>95673662</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>もーつぁ るとぴ</t>
+          <t>はりすた いるんぬ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>早歩きと普通歩きの境界研究</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>講義中に眠くならない方法を研究する</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9478027019</t>
+          <t>2151692012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>90496767</t>
+          <t>82505591</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>めりる すとりゃ</t>
+          <t>よしだま さたろ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>スーパーの値引きタイミング観察</t>
+          <t>机の上の整理（30分だけ）</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>勉強と休憩のバランスを取る</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8977460928</t>
+          <t>2151692012</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>95012302</t>
+          <t>92857074</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>えまま そんりん</t>
+          <t>よしだま さたろ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>電車の発車メロディ研究</t>
+          <t>机の上の整理（30分だけ）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2751889001</t>
+          <t>5836462839</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90653843</t>
+          <t>86299407</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>かわぐてぃ はるにゃ</t>
+          <t>なだる らふぁみゅ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>お菓子のカロリー計算（食べた後）</t>
+          <t>靴ひもを結び直すタイミング研究</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>締切という概念と仲良くなる</t>
+          <t>図書館で寝ない</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8018780257</t>
+          <t>5836462839</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>95768378</t>
+          <t>95066372</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>しょぱん ぴょり</t>
+          <t>なだる らふぁみゅ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>近所の猫の行動観察</t>
+          <t>靴ひもを結び直すタイミング研究</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>発表スライドを前日に完成させる</t>
+          <t>図書館で寝ない</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4357371252</t>
+          <t>7847090015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>91176779</t>
+          <t>88578323</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>りすとん るみゃ</t>
+          <t>はーらん どりん</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>カフェの席取り戦略研究</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>図書館の静けさに慣れる</t>
+          <t>図書館で寝ない</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8224520058</t>
+          <t>7847090015</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>91549389</t>
+          <t>94342395</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ぺどり りんぴ</t>
+          <t>はーらん どりん</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>スーパーの値引きタイミング観察</t>
+          <t>カフェの席取り戦略研究</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>深夜のネットサーフィンを控える（理想）</t>
+          <t>図書館で寝ない</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6480310755</t>
+          <t>7677936335</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93746912</t>
+          <t>80609328</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>べん あふりん</t>
+          <t>きむたくん たくやん</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Google検索の予測変換観察</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>パスワードを覚えられるものにする</t>
+          <t>今年の抱負を来年も思い出す</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6583911310</t>
+          <t>7677936335</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>96011456</t>
+          <t>97666167</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>むばっぺ きゅりん</t>
+          <t>きむたくん たくやん</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>スマホのホーム画面整理</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>今年こそ朝型人間になる（予定）</t>
+          <t>今年の抱負を来年も思い出す</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0301866209</t>
+          <t>4291138460</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>90514484</t>
+          <t>80445152</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>みりー ぼびりん</t>
+          <t>たけうてぃ りょうまる</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ペン回し（成功率30%）</t>
+          <t>信号が変わるタイミング予想</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>パスワードを覚えられるものにする</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5208144369</t>
+          <t>4291138460</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>90111320</t>
+          <t>95265658</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>いけえ りかこぴ</t>
+          <t>たけうてぃ りょうまる</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>信号が変わるタイミング予想</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>講義に5分前に着く人になる</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1973756230</t>
+          <t>5688745612</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>98154857</t>
+          <t>89763787</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ほしのげ げんち</t>
+          <t>えりっく さてぃん</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>早歩きと普通歩きの境界研究</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>寝坊の理由を天候以外にする</t>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1301590939</t>
+          <t>5688745612</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>99482770</t>
+          <t>93289469</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>じょだま いけるん</t>
+          <t>えりっく さてぃん</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>講義に5分前に着く人になる</t>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9484049424</t>
+          <t>5283319832</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>98282607</t>
+          <t>85740441</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ぶらぴと ぴっとん</t>
+          <t>きあぬ りぶりん</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>消しゴムの角を守る</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>研究室のドアをノックする勇気を持つ</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3329879191</t>
+          <t>5283319832</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>94994556</t>
+          <t>91311013</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>きたぐわ けいこちゃ</t>
+          <t>きあぬ りぶりん</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>天気予報の答え合わせ</t>
+          <t>消しゴムの角を守る</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>研究の進捗を月に一度は作る</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0892772298</t>
+          <t>9547056471</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>99349852</t>
+          <t>83079517</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>べねでぃ くとりん</t>
+          <t>まっと でいりん</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>カップ麺の待ち時間アレンジ</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>締切の前日に焦らない生活を目指す</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6056625134</t>
+          <t>9547056471</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>93767436</t>
+          <t>97663602</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ぼるうさ いんたん</t>
+          <t>まっと でいりん</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>天井の模様を眺める</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>積読の本を一冊は読む</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1002495462</t>
+          <t>4770081991</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>98916415</t>
+          <t>85967997</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>くりす へむりん</t>
+          <t>まーご っとりん</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>電車の吊り広告を全部読む</t>
+          <t>近所の猫の行動観察</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ノートをちゃんと取る（たぶん）</t>
+          <t>積読の本を一冊は読む</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5397912856</t>
+          <t>4770081991</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>99072052</t>
+          <t>90463977</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>える ふぁにんぬ</t>
+          <t>まーご っとりん</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>スーパーの値引きタイミング観察</t>
+          <t>近所の猫の行動観察</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>研究の進捗を月に一度は作る</t>
+          <t>積読の本を一冊は読む</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7229972588</t>
+          <t>5233604025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>97947365</t>
+          <t>86692035</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ぱすてる るんぴ</t>
+          <t>ろばーと ぱてりん</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,412 +2152,2518 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>USBメモリをなくさない一年にする</t>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1318276249</t>
+          <t>5233604025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>97526525</t>
+          <t>94066915</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>きゅりまり りんぬ</t>
+          <t>ろばーと ぱてりん</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>歩道のタイル模様を追う</t>
+          <t>コンビニコーヒーの濃さ比較</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4709001521</t>
+          <t>8098503681</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>91462747</t>
+          <t>81239428</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ふくだん みらきゅ</t>
+          <t>ながとも ゆうぴょ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>レシートの長さランキング</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>研究室のドアをノックする勇気を持つ</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4149520758</t>
+          <t>8098503681</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>95122801</t>
+          <t>94420989</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>さかぐてぃ けんたろぴ</t>
+          <t>ながとも ゆうぴょ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ペットボトルのラベル研究</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5989834735</t>
+          <t>3672453456</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>93283594</t>
+          <t>89508708</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>どびゅっし ゅりん</t>
+          <t>やまだて つとん</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>YouTubeおすすめの深掘り</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5885388060</t>
+          <t>3672453456</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>90302590</t>
+          <t>97726754</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>すだまちゃ まさきゅ</t>
+          <t>やまだて つとん</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>雨が降りそうかどうかの体感予測</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>寝坊の理由を天候以外にする</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1447507810</t>
+          <t>7647221686</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>92422894</t>
+          <t>80746018</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>もりなな ぴょん</t>
+          <t>でんぜる わしりん</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>天井の模様を眺める</t>
+          <t>Google検索の予測変換観察</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>机の引き出しの化石を整理する</t>
+          <t>机の上を週に一度は片付ける</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1996851040</t>
+          <t>7647221686</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>90919775</t>
+          <t>93607789</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>しょーん めんりん</t>
+          <t>でんぜる わしりん</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>Google検索の予測変換観察</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>研究室の椅子を壊さない</t>
+          <t>机の上を週に一度は片付ける</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8272778455</t>
+          <t>2576800319</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>95619961</t>
+          <t>85449279</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>じぇにふぁ ろれみゅ</t>
+          <t>うぃる すみりん</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>研究室のドアをノックする勇気を持つ</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3384968416</t>
+          <t>2576800319</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>90041840</t>
+          <t>99055264</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ねいまー るりん</t>
+          <t>うぃる すみりん</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>雲の形の解釈</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>課題のファイル名をわかりやすくする</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1694523937</t>
+          <t>4484286741</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>91142538</t>
+          <t>82044661</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ありあな ぐらぴょ</t>
+          <t>まーらー るぴょ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>スーパーの値引きタイミング観察</t>
+          <t>電車の発車メロディ研究</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>ToDoリストをToDoneリストにする</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6461961544</t>
+          <t>4484286741</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>97993510</t>
+          <t>96598836</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>こーるど ぷれりん</t>
+          <t>まーらー るぴょ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>エアコンの最適温度探し</t>
+          <t>電車の発車メロディ研究</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>昼夜逆転を月に一度は直す</t>
+          <t>ToDoリストをToDoneリストにする</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1993810950</t>
+          <t>7242289444</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>96123779</t>
+          <t>82520910</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>まーらー るぴょ</t>
+          <t>ろばー とぱりん</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>コンビニの新商品チェック</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>パソコンのバックアップを取る</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4662150869</t>
+          <t>7242289444</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>97706335</t>
+          <t>98877977</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ぶらっど ぴょりん</t>
+          <t>ろばー とぱりん</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3080831276</t>
+          <t>7399328359</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>98536163</t>
+          <t>85710069</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>よしだま さたろ</t>
+          <t>ねいまー るりん</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>早歩きと普通歩きの境界研究</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>メールの返信を24時間以内にする</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7846193536</t>
+          <t>7399328359</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>95571403</t>
+          <t>99752937</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ががれで ぃみゅ</t>
+          <t>ねいまー るりん</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>コーヒーを冷ましすぎる</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>メールの返信を24時間以内にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>6008024644</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>87806189</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>みとま りんぴょ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ToDoリストをToDoneリストにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>6008024644</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>90402608</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>みとま りんぴょ</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ToDoリストをToDoneリストにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>9894780270</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>80131345</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>いしはり さとみん</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>エレベーターの待ち時間観測</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>講義に出る回数を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>9894780270</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>93648086</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>いしはり さとみん</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>エレベーターの待ち時間観測</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>講義に出る回数を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>8235556337</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>82673883</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>あんどりゅ りんふ</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>メールの件名を考えすぎる</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>課題のファイル名をわかりやすくする</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8235556337</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>92759740</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>あんどりゅ りんふ</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>メールの件名を考えすぎる</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>課題のファイル名をわかりやすくする</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7035201019</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>85873421</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>すだまちゃ まさきゅ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>エレベーターを使わず階段を使う日を作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7035201019</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>90532363</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>すだまちゃ まさきゅ</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>エレベーターを使わず階段を使う日を作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1503018662</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>86219737</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>さらー りんみゅ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>コーヒーを冷ましすぎる</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>レポートの誤字を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1503018662</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>97520128</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>さらー りんみゅ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>コーヒーを冷ましすぎる</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>レポートの誤字を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>6517348736</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>85685668</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>むばっぺ きゅりん</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>家の周りを一周する</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>プレゼンで「えー」を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6517348736</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>97025442</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>むばっぺ きゅりん</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>家の周りを一周する</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>プレゼンで「えー」を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4840366967</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>86392257</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>てぃも しゃらりん</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>YouTubeおすすめの深掘り</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>友達の課題の進み具合を見て焦らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4840366967</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>94858955</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>てぃも しゃらりん</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>YouTubeおすすめの深掘り</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>友達の課題の進み具合を見て焦らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0539705672</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>80146601</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>こぺるに くすみゅ</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>レシートの長さランキング</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>机の引き出しの化石を整理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0539705672</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>97435375</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>こぺるに くすみゅ</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>レシートの長さランキング</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>机の引き出しの化石を整理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>7258853880</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>82588569</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>だるびしゅ ゆうにゃ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>近所の猫の行動観察</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>研究室の椅子を壊さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>7258853880</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>97618199</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>だるびしゅ ゆうにゃ</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>近所の猫の行動観察</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>研究室の椅子を壊さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1227970565</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>84621199</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>じょーじ くるりん</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ペン回し（成功率30%）</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>机の周りのケーブルを整理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1227970565</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>98252546</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>じょーじ くるりん</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ペン回し（成功率30%）</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>机の周りのケーブルを整理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3369250795</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>81445916</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>よしだ りんちゃ</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>コンビニコーヒーの濃さ比較</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>講義に出る回数を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3369250795</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>95522319</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>よしだ りんちゃ</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>コンビニコーヒーの濃さ比較</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>講義に出る回数を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1192004381</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>87465900</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>らいあん ごすりん</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>新しいショートカットキー探し</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>システムのログインパスワードを忘れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1192004381</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>94303464</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>らいあん ごすりん</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>新しいショートカットキー探し</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2782245200</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>80024954</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>さんどら ぶるぴ</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>電車の中で立ち位置最適化</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>講義中に眠くならない方法を研究する</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2782245200</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>96939429</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>さんどら ぶるぴ</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>電車の中で立ち位置最適化</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>講義中に眠くならない方法を研究する</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4252081443</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>84100189</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>りあーな ぴょんぬ</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>天気予報の答え合わせ</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>研究テーマを説明できるようになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4252081443</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>90592773</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>りあーな ぴょんぬ</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>天気予報の答え合わせ</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>研究テーマを説明できるようになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1991306145</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>86913702</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>きゅりまり りんぬ</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>メールの件名を考えすぎる</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>プレゼンで「えー」を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1991306145</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>99575783</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>きゅりまり りんぬ</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>メールの件名を考えすぎる</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>プレゼンで「えー」を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>5890577055</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>85935034</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>じぇな おてりん</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ノートをちゃんと取る（たぶん）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>5890577055</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>98972094</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>じぇな おてりん</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>キーボードの掃除（気が向いたとき）</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ノートをちゃんと取る（たぶん）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>8271512015</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>80861119</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>じゅりあ ろばりん</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>エレベーターを使わず階段を使う日を作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>8271512015</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>91567310</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>じゅりあ ろばりん</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>エレベーターを使わず階段を使う日を作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>8708118916</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>84050530</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>じぇにふぁ ろれみゅ</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>コーヒーを飲みすぎない</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>8708118916</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>90668055</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>じぇにふぁ ろれみゅ</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>コーヒーを飲みすぎない</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>5845407206</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>85127682</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>しょぱん ぴょり</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>イヤホンの絡まり解消</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>なんとか無事に一年を乗り切る</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>5845407206</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>93529664</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>しょぱん ぴょり</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>イヤホンの絡まり解消</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>なんとか無事に一年を乗り切る</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1047080176</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>83015909</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ればんど ふすりん</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>お菓子のカロリー計算（食べた後）</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1047080176</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>91456228</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ればんど ふすりん</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>お菓子のカロリー計算（食べた後）</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3942269375</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>80010070</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>きたぐわ けいこちゃ</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>電車の中で立ち位置最適化</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>研究テーマを説明できるようになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3942269375</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>96769401</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>きたぐわ けいこちゃ</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>電車の中で立ち位置最適化</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>研究テーマを説明できるようになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>4176332408</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>86461961</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>えま すとんり</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>エアコンの最適温度探し</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>講義に出る回数を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>4176332408</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>90373128</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>えま すとんり</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>エアコンの最適温度探し</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>講義に出る回数を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2071644288</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>81918977</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>とむ ほらりん</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>雨が降りそうかどうかの体感予測</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>研究室の椅子を壊さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2071644288</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>92256962</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>とむ ほらりん</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>雨が降りそうかどうかの体感予測</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>研究室の椅子を壊さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>6075175194</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>87846193</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>おりびあ ころりん</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>スマホのバッテリー節約術研究</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>データを消してから後悔しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>6075175194</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>98649219</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>おりびあ ころりん</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>スマホのバッテリー節約術研究</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>データを消してから後悔しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>5650317293</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>80137754</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>めりる すとりゃ</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ノートの1ページ目をきれいに書く</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>5650317293</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>98551862</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>めりる すとりゃ</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ノートの1ページ目をきれいに書く</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>システムのログインパスワードを忘れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>7896715813</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>85549089</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>くりす へむりん</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>コンビニの新商品チェック</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>朝ごはんを食べる日を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>7896715813</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>92999042</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>くりす へむりん</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>コンビニの新商品チェック</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>朝ごはんを食べる日を増やす</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2983686511</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>83999371</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>とびー まぐりん</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>消しゴムの角を守る</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>研究室のドアをノックする勇気を持つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2983686511</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>92290075</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>とびー まぐりん</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>消しゴムの角を守る</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>研究室のドアをノックする勇気を持つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3613628980</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>89286314</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>すずきせ いやたん</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>電車の吊り広告を全部読む</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>3613628980</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>98967375</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>すずきせ いやたん</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>電車の吊り広告を全部読む</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>課題を提出してから安心して寝る</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>8496681051</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>82594264</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>たき りんぴ</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>家の周りを一周する</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>8496681051</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>98766191</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>たき りんぴ</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>家の周りを一周する</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>4538005222</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>87792394</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>さかぐてぃ けんたろぴ</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>YouTubeおすすめの深掘り</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>図書館の静けさに慣れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>4538005222</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>93544696</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>さかぐてぃ けんたろぴ</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>YouTubeおすすめの深掘り</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>図書館の静けさに慣れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1830165872</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>85369222</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>もどりち るりん</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>目覚ましのスヌーズ回数管理</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>締切という概念と仲良くなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1830165872</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>95085802</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>もどりち るりん</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>目覚ましのスヌーズ回数管理</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>締切という概念と仲良くなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>9148214718</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>84864653</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>あん ねはさりん</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>カレンダーの祝日配置チェック</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>学食の新メニューを全部試す</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>9148214718</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>98964464</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>あん ねはさりん</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>カレンダーの祝日配置チェック</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>学食の新メニューを全部試す</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>4156195615</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>88708599</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>びよんせ るんちゃ</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>電車の吊り広告を全部読む</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>図書館で寝ない</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>4156195615</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>97967628</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>びよんせ るんちゃ</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>電車の吊り広告を全部読む</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>図書館で寝ない</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>8627518890</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>86885931</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ぱすてる るんぴ</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>近所の猫の行動観察</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>「あとでやる」を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>8627518890</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>96999117</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ぱすてる るんぴ</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>近所の猫の行動観察</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>「あとでやる」を減らす</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>6163907205</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>88102249</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ながさま まさみん</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>お菓子のカロリー計算（食べた後）</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>講義の質問を一度はしてみる</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>6163907205</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>92678829</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ながさま まさみん</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>お菓子のカロリー計算（食べた後）</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>講義の質問を一度はしてみる</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2695741483</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>89791285</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>もどりち るかりん</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>天井の模様を眺める</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>机の周りのケーブルを整理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2695741483</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>95886768</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>もどりち るかりん</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>天井の模様を眺める</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>机の周りのケーブルを整理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>5363649378</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>83909838</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>らべるん みゃ</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>冷蔵庫の中を定期巡回する</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>USBメモリをなくさない一年にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>5363649378</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>91803905</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>らべるん みゃ</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>冷蔵庫の中を定期巡回する</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>USBメモリをなくさない一年にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>6904592348</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>80722997</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>しどに すうぇり</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ノートをちゃんと取る（たぶん）</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>6904592348</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>97898519</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>しどに すうぇり</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>新しいボールペンの試し書き</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>ノートをちゃんと取る（たぶん）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>6147116275</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>80184530</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>おおさか なみりん</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>イヤホンの絡まり解消</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>研究テーマを説明できるようになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>6147116275</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>95912833</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>おおさか なみりん</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>イヤホンの絡まり解消</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>

--- a/src/make_dummy_data/登録学生一覧.xlsx
+++ b/src/make_dummy_data/登録学生一覧.xlsx
@@ -458,179 +458,179 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4356302180</t>
+          <t>3569954554</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88289817</t>
+          <t>89819383</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>おおいずみ ひろしぇ</t>
+          <t>いけえ りかこぴ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>家の周りを一周する</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>シラバスをちゃんと読む</t>
+          <t>机の上を週に一度は片付ける</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4356302180</t>
+          <t>3569954554</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90481394</t>
+          <t>91840217</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>おおいずみ ひろしぇ</t>
+          <t>いけえ りかこぴ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>家の周りを一周する</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>シラバスをちゃんと読む</t>
+          <t>机の上を週に一度は片付ける</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2201200418</t>
+          <t>9667537211</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84952075</t>
+          <t>85388687</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>れおなる どりん</t>
+          <t>ふろーれ んすぴ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>家の周りを一周する</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>昼夜逆転を月に一度は直す</t>
+          <t>締切の前日に焦らない生活を目指す</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2201200418</t>
+          <t>9667537211</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>94310102</t>
+          <t>94459564</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>れおなる どりん</t>
+          <t>ふろーれ んすぴ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>家の周りを一周する</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>昼夜逆転を月に一度は直す</t>
+          <t>締切の前日に焦らない生活を目指す</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8434287215</t>
+          <t>2581440473</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>86249761</t>
+          <t>83581455</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ていらー すうぃりん</t>
+          <t>けいしー ましゅりん</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>自販機のラインナップ分析</t>
+          <t>エスカレーターで立ち位置を考える</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>友達の課題の進み具合を見て焦らない</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8434287215</t>
+          <t>2581440473</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90524669</t>
+          <t>94322247</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ていらー すうぃりん</t>
+          <t>けいしー ましゅりん</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>自販機のラインナップ分析</t>
+          <t>エスカレーターで立ち位置を考える</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>友達の課題の進み具合を見て焦らない</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4079935100</t>
+          <t>1155974911</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>88368367</t>
+          <t>89650384</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ていすう ふとちゃ</t>
+          <t>べねでぃ くとりん</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,24 +640,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>「あとでやる」を減らす</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4079935100</t>
+          <t>1155974911</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>96486745</t>
+          <t>90689932</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ていすう ふとちゃ</t>
+          <t>べねでぃ くとりん</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,510 +667,510 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>「あとでやる」を減らす</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9919968510</t>
+          <t>8707686945</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>82531180</t>
+          <t>81107058</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>こーるど ぷれりん</t>
+          <t>ていらー すうぃりん</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>スマホのバッテリー節約術研究</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>講義の質問を一度はしてみる</t>
+          <t>机の引き出しの化石を整理する</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9919968510</t>
+          <t>8707686945</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>96807885</t>
+          <t>95259775</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>こーるど ぷれりん</t>
+          <t>ていらー すうぃりん</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>スマホのバッテリー節約術研究</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>講義の質問を一度はしてみる</t>
+          <t>机の引き出しの化石を整理する</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6912396492</t>
+          <t>2988397052</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>82337490</t>
+          <t>89353105</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>さかもとは やとりん</t>
+          <t>たかなし さらら</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ペットボトルのラベル研究</t>
+          <t>レシートの長さランキング</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6912396492</t>
+          <t>2988397052</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>94274525</t>
+          <t>96383157</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>さかもとは やとりん</t>
+          <t>たかなし さらら</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ペットボトルのラベル研究</t>
+          <t>レシートの長さランキング</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9510146274</t>
+          <t>7314495974</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>88814174</t>
+          <t>89875799</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>やまじゃき けんとん</t>
+          <t>がりれお るんた</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>電車の発車メロディ研究</t>
+          <t>カフェの席取り戦略研究</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>深夜のネットサーフィンを控える（理想）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9510146274</t>
+          <t>7314495974</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>97709106</t>
+          <t>98208090</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>やまじゃき けんとん</t>
+          <t>がりれお るんた</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>電車の発車メロディ研究</t>
+          <t>カフェの席取り戦略研究</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>深夜のネットサーフィンを控える（理想）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4033437086</t>
+          <t>9238500505</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>83968796</t>
+          <t>81063120</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>なただり りんぴょ</t>
+          <t>むばっぺ きゅりん</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>深夜のネットサーフィンを控える（理想）</t>
+          <t>締切の存在を忘れない</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4033437086</t>
+          <t>9238500505</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>93578742</t>
+          <t>94131461</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>なただり りんぴょ</t>
+          <t>むばっぺ きゅりん</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>おにぎりの具ランキング更新</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>深夜のネットサーフィンを控える（理想）</t>
+          <t>締切の存在を忘れない</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0593019235</t>
+          <t>6699172954</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>83286719</t>
+          <t>86636641</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>すあれす りんぴょ</t>
+          <t>そんふん みんりん</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>早歩きと普通歩きの境界研究</t>
+          <t>ペットボトルのラベル研究</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>友達の課題の進み具合を見て焦らない</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0593019235</t>
+          <t>6699172954</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91442685</t>
+          <t>94020785</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>すあれす りんぴょ</t>
+          <t>そんふん みんりん</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>早歩きと普通歩きの境界研究</t>
+          <t>ペットボトルのラベル研究</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>友達の課題の進み具合を見て焦らない</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3779815485</t>
+          <t>0150092541</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>86586801</t>
+          <t>84395056</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ひゅー じゃくりん</t>
+          <t>あらがち ゆいりん</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>エスカレーターで立ち位置を考える</t>
+          <t>自販機のラインナップ分析</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3779815485</t>
+          <t>0150092541</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>91405223</t>
+          <t>99672751</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ひゅー じゃくりん</t>
+          <t>あらがち ゆいりん</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>エスカレーターで立ち位置を考える</t>
+          <t>自販機のラインナップ分析</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1029201825</t>
+          <t>8568696141</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>82431523</t>
+          <t>85160639</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>くろーす りんぬ</t>
+          <t>じぇいく ぎれりん</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>メールの件名を考えすぎる</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>なんとか無事に一年を乗り切る</t>
+          <t>昼夜逆転を月に一度は直す</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1029201825</t>
+          <t>8568696141</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>95944747</t>
+          <t>92232372</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>くろーす りんぬ</t>
+          <t>じぇいく ぎれりん</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>メールの件名を考えすぎる</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>なんとか無事に一年を乗り切る</t>
+          <t>昼夜逆転を月に一度は直す</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4259232515</t>
+          <t>4906064964</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>86314208</t>
+          <t>83977448</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>でびっど べかりん</t>
+          <t>あでるる ぴょみ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>家の周りを一周する</t>
+          <t>イヤホンの絡まり解消</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4259232515</t>
+          <t>4906064964</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>95482699</t>
+          <t>91437772</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>でびっど べかりん</t>
+          <t>あでるる ぴょみ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>家の周りを一周する</t>
+          <t>イヤホンの絡まり解消</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>コーヒーを飲みすぎない</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1615918261</t>
+          <t>5307963592</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>82752501</t>
+          <t>85626545</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>むらかみ むねきゅん</t>
+          <t>あんじぇり なりゅ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>自販機のラインナップ分析</t>
+          <t>エアコンの最適温度探し</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>勉強と休憩のバランスを取る</t>
+          <t>データを消してから後悔しない</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1615918261</t>
+          <t>5307963592</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>93714532</t>
+          <t>91321855</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>むらかみ むねきゅん</t>
+          <t>あんじぇり なりゅ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>自販機のラインナップ分析</t>
+          <t>エアコンの最適温度探し</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>勉強と休憩のバランスを取る</t>
+          <t>データを消してから後悔しない</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3450123020</t>
+          <t>7760494092</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>81691829</t>
+          <t>87409128</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>もりなな ぴょん</t>
+          <t>うぃる すみりん</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,24 +1180,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>講義に5分前に着く人になる</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3450123020</t>
+          <t>7760494092</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>92470093</t>
+          <t>96433877</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>もりなな ぴょん</t>
+          <t>うぃる すみりん</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,456 +1207,456 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>講義に5分前に着く人になる</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4681791561</t>
+          <t>6655796998</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89687518</t>
+          <t>89983907</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>べんぜま りんる</t>
+          <t>まーらー るぴょ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>スーパーの値引きタイミング観察</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>昼夜逆転を月に一度は直す</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4681791561</t>
+          <t>6655796998</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>97309791</t>
+          <t>94845031</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>べんぜま りんる</t>
+          <t>まーらー るぴょ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>スーパーの値引きタイミング観察</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>昼夜逆転を月に一度は直す</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0338939162</t>
+          <t>3190128716</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>84341794</t>
+          <t>84295768</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ががれで ぃみゅ</t>
+          <t>にゅとーん いさりん</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>電車のドア位置研究</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>研究の進捗を月に一度は作る</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0338939162</t>
+          <t>3190128716</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>91831457</t>
+          <t>93994600</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ががれで ぃみゅ</t>
+          <t>にゅとーん いさりん</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>机のガタつき調整</t>
+          <t>電車のドア位置研究</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>研究の進捗を月に一度は作る</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0840753406</t>
+          <t>1884341751</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>84171861</t>
+          <t>83620845</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ありあな ぐらぴょ</t>
+          <t>えどしー らんぴ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>コンビニコーヒーの濃さ比較</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>パスワードを覚えられるものにする</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0840753406</t>
+          <t>1884341751</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>97199041</t>
+          <t>93104762</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ありあな ぐらぴょ</t>
+          <t>えどしー らんぴ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>コンビニコーヒーの濃さ比較</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>パスワードを覚えられるものにする</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7286362653</t>
+          <t>5399271539</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>84988098</t>
+          <t>81477200</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>どびゅっし ゅりん</t>
+          <t>かわぐてぃ はるにゃ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>講義の質問を一度はしてみる</t>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7286362653</t>
+          <t>5399271539</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>96049623</t>
+          <t>90407417</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>どびゅっし ゅりん</t>
+          <t>かわぐてぃ はるにゃ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>講義の質問を一度はしてみる</t>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2785935012</t>
+          <t>9678037680</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>81131005</t>
+          <t>84759236</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>そんふん みんりん</t>
+          <t>えじそと とまち</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>締切の前日に焦らない生活を目指す</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2785935012</t>
+          <t>9678037680</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>96616215</t>
+          <t>95075857</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>そんふん みんりん</t>
+          <t>えじそと とまち</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>書店で背表紙を読む</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>締切の前日に焦らない生活を目指す</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9365122801</t>
+          <t>0233871846</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>80543919</t>
+          <t>88834586</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>にしじま ひでとん</t>
+          <t>じぇし かちゃり</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>今年こそ朝型人間になる（予定）</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9365122801</t>
+          <t>0233871846</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>94114987</t>
+          <t>95943979</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>にしじま ひでとん</t>
+          <t>じぇし かちゃり</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>今年こそ朝型人間になる（予定）</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3774757058</t>
+          <t>3731258692</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>87424789</t>
+          <t>84446000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ぶらぴと ぴっとん</t>
+          <t>まーく らふりん</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>お菓子のカロリー計算（食べた後）</t>
+          <t>机の上の整理（30分だけ）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>勉強と休憩のバランスを取る</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3774757058</t>
+          <t>3731258692</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>96988445</t>
+          <t>99651056</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ぶらぴと ぴっとん</t>
+          <t>まーく らふりん</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>お菓子のカロリー計算（食べた後）</t>
+          <t>机の上の整理（30分だけ）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>勉強と休憩のバランスを取る</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5660049440</t>
+          <t>6705878242</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>88760914</t>
+          <t>89892052</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>はりすた いるんぬ</t>
+          <t>ぼるうさ いんたん</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>早歩きと普通歩きの境界研究</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>講義中に眠くならない方法を研究する</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5660049440</t>
+          <t>6705878242</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>95673662</t>
+          <t>92245546</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>はりすた いるんぬ</t>
+          <t>ぼるうさ いんたん</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>早歩きと普通歩きの境界研究</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>講義中に眠くならない方法を研究する</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2151692012</t>
+          <t>2181173097</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>82505591</t>
+          <t>84882663</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>よしだま さたろ</t>
+          <t>はまなべ みなみゅ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,24 +1666,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USBメモリをなくさない一年にする</t>
+          <t>「あとでやる」を減らす</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2151692012</t>
+          <t>2181173097</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>92857074</t>
+          <t>92624239</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>よしだま さたろ</t>
+          <t>はまなべ みなみゅ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1693,1806 +1693,1806 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USBメモリをなくさない一年にする</t>
+          <t>「あとでやる」を減らす</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5836462839</t>
+          <t>5554193689</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>86299407</t>
+          <t>83861836</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>なだる らふぁみゅ</t>
+          <t>めりる すとりゃ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>靴ひもを結び直すタイミング研究</t>
+          <t>近所の猫の行動観察</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5836462839</t>
+          <t>5554193689</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>95066372</t>
+          <t>95023662</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>なだる らふぁみゅ</t>
+          <t>めりる すとりゃ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>靴ひもを結び直すタイミング研究</t>
+          <t>近所の猫の行動観察</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>パソコンのアップデートを放置しない</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7847090015</t>
+          <t>0219547920</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>88578323</t>
+          <t>86877083</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>はーらん どりん</t>
+          <t>えんどう りんみゅ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>カフェの席取り戦略研究</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7847090015</t>
+          <t>0219547920</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>94342395</t>
+          <t>99034782</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>はーらん どりん</t>
+          <t>えんどう りんみゅ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>カフェの席取り戦略研究</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7677936335</t>
+          <t>9619813605</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>80609328</t>
+          <t>88055449</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>きむたくん たくやん</t>
+          <t>ればんど ふすりん</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>雲の形の解釈</t>
+          <t>スーパーの値引きタイミング観察</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>今年の抱負を来年も思い出す</t>
+          <t>パソコンのバックアップを取る</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7677936335</t>
+          <t>9619813605</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>97666167</t>
+          <t>98519606</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>きむたくん たくやん</t>
+          <t>ればんど ふすりん</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>雲の形の解釈</t>
+          <t>スーパーの値引きタイミング観察</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>今年の抱負を来年も思い出す</t>
+          <t>パソコンのバックアップを取る</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4291138460</t>
+          <t>8428333614</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>80445152</t>
+          <t>83512406</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>たけうてぃ りょうまる</t>
+          <t>はにゅう ゆづりゅ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>信号が変わるタイミング予想</t>
+          <t>エアコンの最適温度探し</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>レポートの誤字を減らす</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4291138460</t>
+          <t>8428333614</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>95265658</t>
+          <t>98026958</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>たけうてぃ りょうまる</t>
+          <t>はにゅう ゆづりゅ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>信号が変わるタイミング予想</t>
+          <t>エアコンの最適温度探し</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>レポートの誤字を減らす</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5688745612</t>
+          <t>0331185755</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>89763787</t>
+          <t>86396548</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>えりっく さてぃん</t>
+          <t>えまま そんりん</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>雲の形の解釈</t>
+          <t>カップ麺の待ち時間アレンジ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>パソコンのアップデートを放置しない</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5688745612</t>
+          <t>0331185755</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>93289469</t>
+          <t>92877633</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>えりっく さてぃん</t>
+          <t>えまま そんりん</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>雲の形の解釈</t>
+          <t>カップ麺の待ち時間アレンジ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>パソコンのアップデートを放置しない</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5283319832</t>
+          <t>3392692042</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>85740441</t>
+          <t>86340102</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>きあぬ りぶりん</t>
+          <t>ろなくり どるん</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>消しゴムの角を守る</t>
+          <t>ノートの1ページ目をきれいに書く</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5283319832</t>
+          <t>3392692042</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>91311013</t>
+          <t>92577411</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>きあぬ りぶりん</t>
+          <t>ろなくり どるん</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>消しゴムの角を守る</t>
+          <t>ノートの1ページ目をきれいに書く</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9547056471</t>
+          <t>3546216670</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>83079517</t>
+          <t>87324059</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>まっと でいりん</t>
+          <t>でびっど べかりん</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>カレンダーの祝日配置チェック</t>
+          <t>自販機のラインナップ分析</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9547056471</t>
+          <t>3546216670</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>97663602</t>
+          <t>90445251</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>まっと でいりん</t>
+          <t>でびっど べかりん</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>カレンダーの祝日配置チェック</t>
+          <t>自販機のラインナップ分析</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4770081991</t>
+          <t>1522223552</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>85967997</t>
+          <t>81546747</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>まーご っとりん</t>
+          <t>でぃかぷり おれおん</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>近所の猫の行動観察</t>
+          <t>エレベーターの待ち時間観測</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>積読の本を一冊は読む</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4770081991</t>
+          <t>1522223552</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90463977</t>
+          <t>99401770</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>まーご っとりん</t>
+          <t>でぃかぷり おれおん</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>近所の猫の行動観察</t>
+          <t>エレベーターの待ち時間観測</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>積読の本を一冊は読む</t>
+          <t>シラバスをちゃんと読む</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5233604025</t>
+          <t>2063884772</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>86692035</t>
+          <t>85472613</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ろばーと ぱてりん</t>
+          <t>いしはり さとみん</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>信号が変わるタイミング予想</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wi-Fiが遅いときにまず自分を疑う</t>
+          <t>プリンタの紙詰まりを自分で直せるようになる</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5233604025</t>
+          <t>2063884772</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>94066915</t>
+          <t>95680679</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ろばーと ぱてりん</t>
+          <t>いしはり さとみん</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>信号が変わるタイミング予想</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wi-Fiが遅いときにまず自分を疑う</t>
+          <t>プリンタの紙詰まりを自分で直せるようになる</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8098503681</t>
+          <t>0565547372</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>81239428</t>
+          <t>81374564</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ながとも ゆうぴょ</t>
+          <t>わおたに しょうたいむ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>冷蔵庫の中を定期巡回する</t>
+          <t>消しゴムの角を守る</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gitでやらかさない</t>
+          <t>プレゼンで「えー」を減らす</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8098503681</t>
+          <t>0565547372</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>94420989</t>
+          <t>93119860</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ながとも ゆうぴょ</t>
+          <t>わおたに しょうたいむ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>冷蔵庫の中を定期巡回する</t>
+          <t>消しゴムの角を守る</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gitでやらかさない</t>
+          <t>プレゼンで「えー」を減らす</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3672453456</t>
+          <t>3227082954</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>89508708</t>
+          <t>85522804</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>やまだて つとん</t>
+          <t>はりー すたぴょ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3672453456</t>
+          <t>3227082954</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>97726754</t>
+          <t>98339953</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>やまだて つとん</t>
+          <t>はりー すたぴょ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>おにぎりの具ランキング更新</t>
+          <t>雲の形の解釈</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7647221686</t>
+          <t>3500847521</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>80746018</t>
+          <t>83807221</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>でんぜる わしりん</t>
+          <t>しょーん めんりん</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Google検索の予測変換観察</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>机の上を週に一度は片付ける</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7647221686</t>
+          <t>3500847521</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>93607789</t>
+          <t>97801686</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>でんぜる わしりん</t>
+          <t>しょーん めんりん</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Google検索の予測変換観察</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>机の上を週に一度は片付ける</t>
+          <t>講義の質問を一度はしてみる</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2576800319</t>
+          <t>3718807930</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>85449279</t>
+          <t>89215129</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>うぃる すみりん</t>
+          <t>とびー まぐりん</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>カレンダーの祝日配置チェック</t>
+          <t>エレベーターの待ち時間観測</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>ToDoリストをToDoneリストにする</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2576800319</t>
+          <t>3718807930</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>99055264</t>
+          <t>93544230</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>うぃる すみりん</t>
+          <t>とびー まぐりん</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>カレンダーの祝日配置チェック</t>
+          <t>エレベーターの待ち時間観測</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>ToDoリストをToDoneリストにする</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4484286741</t>
+          <t>1217126002</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>82044661</t>
+          <t>89403396</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>まーらー るぴょ</t>
+          <t>ねいまる るぴょ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>電車の発車メロディ研究</t>
+          <t>ノートの1ページ目をきれいに書く</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ToDoリストをToDoneリストにする</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4484286741</t>
+          <t>1217126002</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>96598836</t>
+          <t>95167661</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>まーらー るぴょ</t>
+          <t>ねいまる るぴょ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>電車の発車メロディ研究</t>
+          <t>ノートの1ページ目をきれいに書く</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ToDoリストをToDoneリストにする</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7242289444</t>
+          <t>3801957825</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>82520910</t>
+          <t>85727095</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ろばー とぱりん</t>
+          <t>なただり りんぴょ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>Wi‑Fiの電波強度チェック</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>シラバスをちゃんと読む</t>
+          <t>寝坊の理由を天候以外にする</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7242289444</t>
+          <t>3801957825</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>98877977</t>
+          <t>96913032</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ろばー とぱりん</t>
+          <t>なただり りんぴょ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>Wi‑Fiの電波強度チェック</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>シラバスをちゃんと読む</t>
+          <t>寝坊の理由を天候以外にする</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7399328359</t>
+          <t>2621440707</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>85710069</t>
+          <t>86064828</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ねいまー るりん</t>
+          <t>えみりー ぶらりん</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>目覚ましのスヌーズ回数管理</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>メールの返信を24時間以内にする</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7399328359</t>
+          <t>2621440707</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>99752937</t>
+          <t>93642325</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ねいまー るりん</t>
+          <t>えみりー ぶらりん</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>目覚ましのスヌーズ回数管理</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>メールの返信を24時間以内にする</t>
+          <t>研究テーマを説明できるようになる</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6008024644</t>
+          <t>1829315365</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>87806189</t>
+          <t>89401508</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>みとま りんぴょ</t>
+          <t>べかむで びちゃ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ToDoリストをToDoneリストにする</t>
+          <t>エレベーターを使わず階段を使う日を作る</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6008024644</t>
+          <t>1829315365</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>90402608</t>
+          <t>91404541</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>みとま りんぴょ</t>
+          <t>べかむで びちゃ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>冷蔵庫の中を定期巡回する</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ToDoリストをToDoneリストにする</t>
+          <t>エレベーターを使わず階段を使う日を作る</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9894780270</t>
+          <t>6308902443</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>80131345</t>
+          <t>88260086</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>いしはり さとみん</t>
+          <t>あやせる はるかるん</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>エレベーターの待ち時間観測</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9894780270</t>
+          <t>6308902443</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>93648086</t>
+          <t>94728950</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>いしはり さとみん</t>
+          <t>あやせる はるかるん</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>エレベーターの待ち時間観測</t>
+          <t>コーヒーを冷ましすぎる</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8235556337</t>
+          <t>2627472241</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>82673883</t>
+          <t>85773812</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>あんどりゅ りんふ</t>
+          <t>まついひ できゅ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>メールの件名を考えすぎる</t>
+          <t>電車のドア位置研究</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>課題のファイル名をわかりやすくする</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8235556337</t>
+          <t>2627472241</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>92759740</t>
+          <t>96016606</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>あんどりゅ りんふ</t>
+          <t>まついひ できゅ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>メールの件名を考えすぎる</t>
+          <t>電車のドア位置研究</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>課題のファイル名をわかりやすくする</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7035201019</t>
+          <t>2958293117</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>85873421</t>
+          <t>88990964</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>すだまちゃ まさきゅ</t>
+          <t>びよんせ るんちゃ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>信号が変わるタイミング予想</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>エレベーターを使わず階段を使う日を作る</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7035201019</t>
+          <t>2958293117</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>90532363</t>
+          <t>90006505</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>すだまちゃ まさきゅ</t>
+          <t>びよんせ るんちゃ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>信号が変わるタイミング予想</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>エレベーターを使わず階段を使う日を作る</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1503018662</t>
+          <t>4001428084</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>86219737</t>
+          <t>88734209</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>さらー りんみゅ</t>
+          <t>おおさか なみりん</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>スマホのホーム画面整理</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>レポートの誤字を減らす</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1503018662</t>
+          <t>4001428084</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>97520128</t>
+          <t>90449550</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>さらー りんみゅ</t>
+          <t>おおさか なみりん</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>コーヒーを冷ましすぎる</t>
+          <t>スマホのホーム画面整理</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>レポートの誤字を減らす</t>
+          <t>勉強と休憩のバランスを取る</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6517348736</t>
+          <t>0230295576</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>85685668</t>
+          <t>89976038</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>むばっぺ きゅりん</t>
+          <t>にこーる きどりん</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>家の周りを一周する</t>
+          <t>コンビニの新商品チェック</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>プレゼンで「えー」を減らす</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6517348736</t>
+          <t>0230295576</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>97025442</t>
+          <t>99036913</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>むばっぺ きゅりん</t>
+          <t>にこーる きどりん</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>家の周りを一周する</t>
+          <t>コンビニの新商品チェック</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>プレゼンで「えー」を減らす</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4840366967</t>
+          <t>2352236136</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>86392257</t>
+          <t>83358113</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>てぃも しゃらりん</t>
+          <t>りあーな ぴょんぬ</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>YouTubeおすすめの深掘り</t>
+          <t>エスカレーターで立ち位置を考える</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>友達の課題の進み具合を見て焦らない</t>
+          <t>積読の本を一冊は読む</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4840366967</t>
+          <t>2352236136</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>94858955</t>
+          <t>98682746</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>てぃも しゃらりん</t>
+          <t>りあーな ぴょんぬ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>YouTubeおすすめの深掘り</t>
+          <t>エスカレーターで立ち位置を考える</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>友達の課題の進み具合を見て焦らない</t>
+          <t>積読の本を一冊は読む</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0539705672</t>
+          <t>2939798818</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>80146601</t>
+          <t>83681827</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>こぺるに くすみゅ</t>
+          <t>おおいずみ ひろしぇ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>レシートの長さランキング</t>
+          <t>Wi‑Fiの電波強度チェック</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>机の引き出しの化石を整理する</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0539705672</t>
+          <t>2939798818</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>97435375</t>
+          <t>98574775</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>こぺるに くすみゅ</t>
+          <t>おおいずみ ひろしぇ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>レシートの長さランキング</t>
+          <t>Wi‑Fiの電波強度チェック</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>机の引き出しの化石を整理する</t>
+          <t>Gitでやらかさない</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7258853880</t>
+          <t>0295127157</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>82588569</t>
+          <t>88083958</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>だるびしゅ ゆうにゃ</t>
+          <t>える ふぁにんぬ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>近所の猫の行動観察</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>研究室の椅子を壊さない</t>
+          <t>パソコンのバックアップを取る</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7258853880</t>
+          <t>0295127157</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>97618199</t>
+          <t>92932943</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>だるびしゅ ゆうにゃ</t>
+          <t>える ふぁにんぬ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>近所の猫の行動観察</t>
+          <t>机のガタつき調整</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>研究室の椅子を壊さない</t>
+          <t>パソコンのバックアップを取る</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1227970565</t>
+          <t>6804318284</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>84621199</t>
+          <t>88987218</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>じょーじ くるりん</t>
+          <t>すだまちゃ まさきゅ</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ペン回し（成功率30%）</t>
+          <t>次にやることを考える</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>机の周りのケーブルを整理する</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1227970565</t>
+          <t>6804318284</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>98252546</t>
+          <t>98936220</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>じょーじ くるりん</t>
+          <t>すだまちゃ まさきゅ</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ペン回し（成功率30%）</t>
+          <t>次にやることを考える</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>机の周りのケーブルを整理する</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3369250795</t>
+          <t>7950413141</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>81445916</t>
+          <t>82948444</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>よしだ りんちゃ</t>
+          <t>きあぬ りぶりん</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>近所の猫の行動観察</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>課題のファイル名をわかりやすくする</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3369250795</t>
+          <t>7950413141</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>95522319</t>
+          <t>99878853</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>よしだ りんちゃ</t>
+          <t>きあぬ りぶりん</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>コンビニコーヒーの濃さ比較</t>
+          <t>近所の猫の行動観察</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>課題のファイル名をわかりやすくする</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1192004381</t>
+          <t>3837655852</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>87465900</t>
+          <t>83017231</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>らいあん ごすりん</t>
+          <t>くろーす りんぬ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>新しいショートカットキー探し</t>
+          <t>電車のドア位置研究</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>講義に出る回数を増やす</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1192004381</t>
+          <t>3837655852</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>94303464</t>
+          <t>98421660</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>らいあん ごすりん</t>
+          <t>くろーす りんぬ</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>新しいショートカットキー探し</t>
+          <t>電車のドア位置研究</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>講義に出る回数を増やす</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2782245200</t>
+          <t>2082944668</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>80024954</t>
+          <t>87624460</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>さんどら ぶるぴ</t>
+          <t>ほんだけ いすけちゃ</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>電車の中で立ち位置最適化</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>講義中に眠くならない方法を研究する</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2782245200</t>
+          <t>2082944668</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>96939429</t>
+          <t>99420494</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>さんどら ぶるぴ</t>
+          <t>ほんだけ いすけちゃ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>電車の中で立ち位置最適化</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>講義中に眠くならない方法を研究する</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4252081443</t>
+          <t>3438999234</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>84100189</t>
+          <t>88504007</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>りあーな ぴょんぬ</t>
+          <t>あいしゅ たいんるん</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>天気予報の答え合わせ</t>
+          <t>雨が降りそうかどうかの体感予測</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4252081443</t>
+          <t>3438999234</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>90592773</t>
+          <t>97863193</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>りあーな ぴょんぬ</t>
+          <t>あいしゅ たいんるん</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>天気予報の答え合わせ</t>
+          <t>雨が降りそうかどうかの体感予測</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1991306145</t>
+          <t>6116149818</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>86913702</t>
+          <t>87789371</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>きゅりまり りんぬ</t>
+          <t>とみやす りんぬ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>メールの件名を考えすぎる</t>
+          <t>歩道のタイル模様を追う</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>プレゼンで「えー」を減らす</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1991306145</t>
+          <t>6116149818</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>99575783</t>
+          <t>90650407</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>きゅりまり りんぬ</t>
+          <t>とみやす りんぬ</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>メールの件名を考えすぎる</t>
+          <t>歩道のタイル模様を追う</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>プレゼンで「えー」を減らす</t>
+          <t>パスワードを覚えられるものにする</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5890577055</t>
+          <t>5912677696</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>85935034</t>
+          <t>84595474</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>じぇな おてりん</t>
+          <t>さらー りんみゅ</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>次にやることを考える</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ノートをちゃんと取る（たぶん）</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5890577055</t>
+          <t>5912677696</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>98972094</t>
+          <t>91850096</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>じぇな おてりん</t>
+          <t>さらー りんみゅ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>キーボードの掃除（気が向いたとき）</t>
+          <t>次にやることを考える</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ノートをちゃんと取る（たぶん）</t>
+          <t>USBメモリをなくさない一年にする</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8271512015</t>
+          <t>6426056583</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>80861119</t>
+          <t>87806377</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>じゅりあ ろばりん</t>
+          <t>じょーじ くるりん</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>早歩きと普通歩きの境界研究</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>エレベーターを使わず階段を使う日を作る</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8271512015</t>
+          <t>6426056583</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>91567310</t>
+          <t>94203094</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>じゅりあ ろばりん</t>
+          <t>じょーじ くるりん</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>早歩きと普通歩きの境界研究</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>エレベーターを使わず階段を使う日を作る</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8708118916</t>
+          <t>2860400579</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>84050530</t>
+          <t>81104621</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>じぇにふぁ ろれみゅ</t>
+          <t>へんりー かびりん</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3502,24 +3502,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>机の周りのケーブルを整理する</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8708118916</t>
+          <t>2860400579</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>90668055</t>
+          <t>98101987</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>じぇにふぁ ろれみゅ</t>
+          <t>へんりー かびりん</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3529,1141 +3529,1141 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>コーヒーを飲みすぎない</t>
+          <t>机の周りのケーブルを整理する</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5845407206</t>
+          <t>3647687940</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>85127682</t>
+          <t>85599319</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>しょぱん ぴょり</t>
+          <t>ぜんで いやりん</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>イヤホンの絡まり解消</t>
+          <t>Googleマップで遠くの街を散歩</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>なんとか無事に一年を乗り切る</t>
+          <t>寝坊の理由を天候以外にする</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5845407206</t>
+          <t>3647687940</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>93529664</t>
+          <t>95690563</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>しょぱん ぴょり</t>
+          <t>ぜんで いやりん</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>イヤホンの絡まり解消</t>
+          <t>Googleマップで遠くの街を散歩</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>なんとか無事に一年を乗り切る</t>
+          <t>寝坊の理由を天候以外にする</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1047080176</t>
+          <t>3583896431</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>83015909</t>
+          <t>88181550</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ればんど ふすりん</t>
+          <t>べんぜま りんる</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>お菓子のカロリー計算（食べた後）</t>
+          <t>スーパーの値引きタイミング観察</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1047080176</t>
+          <t>3583896431</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>91456228</t>
+          <t>95875200</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ればんど ふすりん</t>
+          <t>べんぜま りんる</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>お菓子のカロリー計算（食べた後）</t>
+          <t>スーパーの値引きタイミング観察</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3942269375</t>
+          <t>0213570673</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>80010070</t>
+          <t>87418272</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>きたぐわ けいこちゃ</t>
+          <t>ばっはん るんみ</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>電車の中で立ち位置最適化</t>
+          <t>スマホのバッテリー節約術研究</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3942269375</t>
+          <t>0213570673</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>96769401</t>
+          <t>93406203</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>きたぐわ けいこちゃ</t>
+          <t>ばっはん るんみ</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>電車の中で立ち位置最適化</t>
+          <t>スマホのバッテリー節約術研究</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4176332408</t>
+          <t>1956762927</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>86461961</t>
+          <t>83614372</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>えま すとんり</t>
+          <t>まーご っとりん</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>エアコンの最適温度探し</t>
+          <t>コンビニの新商品チェック</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4176332408</t>
+          <t>1956762927</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>90373128</t>
+          <t>96506817</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>えま すとんり</t>
+          <t>まーご っとりん</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>エアコンの最適温度探し</t>
+          <t>コンビニの新商品チェック</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>講義に出る回数を増やす</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2071644288</t>
+          <t>9197334271</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>81918977</t>
+          <t>82229078</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>とむ ほらりん</t>
+          <t>だにえる くらりん</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>雨が降りそうかどうかの体感予測</t>
+          <t>Googleマップで遠くの街を散歩</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>研究室の椅子を壊さない</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2071644288</t>
+          <t>9197334271</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>92256962</t>
+          <t>98327020</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>とむ ほらりん</t>
+          <t>だにえる くらりん</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>雨が降りそうかどうかの体感予測</t>
+          <t>Googleマップで遠くの街を散歩</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>研究室の椅子を壊さない</t>
+          <t>朝ごはんを食べる日を増やす</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6075175194</t>
+          <t>6618784276</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>87846193</t>
+          <t>86664813</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>おりびあ ころりん</t>
+          <t>ろばー とぱりん</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>スマホのバッテリー節約術研究</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>データを消してから後悔しない</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6075175194</t>
+          <t>6618784276</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>98649219</t>
+          <t>98443936</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>おりびあ ころりん</t>
+          <t>ろばー とぱりん</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>スマホのバッテリー節約術研究</t>
+          <t>カレンダーの祝日配置チェック</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>データを消してから後悔しない</t>
+          <t>なんとか無事に一年を乗り切る</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5650317293</t>
+          <t>8970542942</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>80137754</t>
+          <t>86826100</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>めりる すとりゃ</t>
+          <t>わーぐな るんちゃ</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ノートの1ページ目をきれいに書く</t>
+          <t>机の上の整理（30分だけ）</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5650317293</t>
+          <t>8970542942</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>98551862</t>
+          <t>91242886</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>めりる すとりゃ</t>
+          <t>わーぐな るんちゃ</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ノートの1ページ目をきれいに書く</t>
+          <t>机の上の整理（30分だけ）</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>システムのログインパスワードを忘れない</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7896715813</t>
+          <t>0741464078</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>85549089</t>
+          <t>80914792</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>くりす へむりん</t>
+          <t>もどりち るりん</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>コンビニの新商品チェック</t>
+          <t>天井の模様を眺める</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7896715813</t>
+          <t>0741464078</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>92999042</t>
+          <t>92807213</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>くりす へむりん</t>
+          <t>もどりち るりん</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>コンビニの新商品チェック</t>
+          <t>天井の模様を眺める</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>朝ごはんを食べる日を増やす</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2983686511</t>
+          <t>1592176838</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>83999371</t>
+          <t>82300577</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>とびー まぐりん</t>
+          <t>がび りんちゃ</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>消しゴムの角を守る</t>
+          <t>電車の吊り広告を全部読む</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>研究室のドアをノックする勇気を持つ</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2983686511</t>
+          <t>1592176838</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>92290075</t>
+          <t>93729161</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>とびー まぐりん</t>
+          <t>がび りんちゃ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>消しゴムの角を守る</t>
+          <t>電車の吊り広告を全部読む</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>研究室のドアをノックする勇気を持つ</t>
+          <t>今年こそ朝型人間になる（予定）</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3613628980</t>
+          <t>6394890094</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>89286314</t>
+          <t>81799623</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>すずきせ いやたん</t>
+          <t>ひろしぇ すずたん</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>電車の吊り広告を全部読む</t>
+          <t>ペン回し（成功率30%）</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3613628980</t>
+          <t>6394890094</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>98967375</t>
+          <t>99132420</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>すずきせ いやたん</t>
+          <t>ひろしぇ すずたん</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>電車の吊り広告を全部読む</t>
+          <t>ペン回し（成功率30%）</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>課題を提出してから安心して寝る</t>
+          <t>友達の課題の進み具合を見て焦らない</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8496681051</t>
+          <t>7270529281</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>82594264</t>
+          <t>86906700</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>たき りんぴ</t>
+          <t>じょだま いけるん</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>家の周りを一周する</t>
+          <t>エスカレーターで立ち位置を考える</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Wi-Fiが遅いときにまず自分を疑う</t>
+          <t>研究室の椅子を壊さない</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8496681051</t>
+          <t>7270529281</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>98766191</t>
+          <t>92734040</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>たき りんぴ</t>
+          <t>じょだま いけるん</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>家の周りを一周する</t>
+          <t>エスカレーターで立ち位置を考える</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Wi-Fiが遅いときにまず自分を疑う</t>
+          <t>研究室の椅子を壊さない</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4538005222</t>
+          <t>9361625765</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>87792394</t>
+          <t>83585610</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>さかぐてぃ けんたろぴ</t>
+          <t>ありあな ぐらぴょ</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>YouTubeおすすめの深掘り</t>
+          <t>キーボードの掃除（気が向いたとき）</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>図書館の静けさに慣れる</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4538005222</t>
+          <t>9361625765</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>93544696</t>
+          <t>90402451</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>さかぐてぃ けんたろぴ</t>
+          <t>ありあな ぐらぴょ</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>YouTubeおすすめの深掘り</t>
+          <t>キーボードの掃除（気が向いたとき）</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>図書館の静けさに慣れる</t>
+          <t>学食の新メニューを全部試す</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1830165872</t>
+          <t>9926712757</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>85369222</t>
+          <t>88697776</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>もどりち るりん</t>
+          <t>ふぇでら ろじゃりん</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>目覚ましのスヌーズ回数管理</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>締切という概念と仲良くなる</t>
+          <t>研究室のドアをノックする勇気を持つ</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1830165872</t>
+          <t>9926712757</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>95085802</t>
+          <t>99711864</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>もどりち るりん</t>
+          <t>ふぇでら ろじゃりん</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>目覚ましのスヌーズ回数管理</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>締切という概念と仲良くなる</t>
+          <t>研究室のドアをノックする勇気を持つ</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>9148214718</t>
+          <t>1626915228</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>84864653</t>
+          <t>81540389</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>あん ねはさりん</t>
+          <t>すずきせ いやたん</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>カレンダーの祝日配置チェック</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>9148214718</t>
+          <t>1626915228</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>98964464</t>
+          <t>94370468</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>あん ねはさりん</t>
+          <t>すずきせ いやたん</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>カレンダーの祝日配置チェック</t>
+          <t>お菓子のカロリー計算（食べた後）</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>学食の新メニューを全部試す</t>
+          <t>図書館の静けさに慣れる</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4156195615</t>
+          <t>2053837880</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>88708599</t>
+          <t>85675086</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>びよんせ るんちゃ</t>
+          <t>さかぐてぃ けんたろぴ</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>電車の吊り広告を全部読む</t>
+          <t>歩道のタイル模様を追う</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>スマホを見ない時間を一日5分作る</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4156195615</t>
+          <t>2053837880</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>97967628</t>
+          <t>97193980</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>びよんせ るんちゃ</t>
+          <t>さかぐてぃ けんたろぴ</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>電車の吊り広告を全部読む</t>
+          <t>歩道のタイル模様を追う</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>図書館で寝ない</t>
+          <t>スマホを見ない時間を一日5分作る</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8627518890</t>
+          <t>3956139734</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>86885931</t>
+          <t>81544437</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ぱすてる るんぴ</t>
+          <t>だこた じょんり</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>近所の猫の行動観察</t>
+          <t>キーボードの掃除（気が向いたとき）</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>「あとでやる」を減らす</t>
+          <t>レポートを提出期限より前に出す経験をする</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8627518890</t>
+          <t>3956139734</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>96999117</t>
+          <t>97415748</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ぱすてる るんぴ</t>
+          <t>だこた じょんり</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>近所の猫の行動観察</t>
+          <t>キーボードの掃除（気が向いたとき）</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>「あとでやる」を減らす</t>
+          <t>レポートを提出期限より前に出す経験をする</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6163907205</t>
+          <t>2940353976</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>88102249</t>
+          <t>81885352</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ながさま まさみん</t>
+          <t>とむるん くるーちゃ</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>お菓子のカロリー計算（食べた後）</t>
+          <t>イヤホンの絡まり解消</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>講義の質問を一度はしてみる</t>
+          <t>ToDoリストをToDoneリストにする</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6163907205</t>
+          <t>2940353976</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>92678829</t>
+          <t>96486729</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ながさま まさみん</t>
+          <t>とむるん くるーちゃ</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>お菓子のカロリー計算（食べた後）</t>
+          <t>イヤホンの絡まり解消</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>講義の質問を一度はしてみる</t>
+          <t>ToDoリストをToDoneリストにする</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2695741483</t>
+          <t>0258361667</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>89791285</t>
+          <t>83320141</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>もどりち るかりん</t>
+          <t>えりっく さてぃん</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>天井の模様を眺める</t>
+          <t>メールの件名を考えすぎる</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>机の周りのケーブルを整理する</t>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2695741483</t>
+          <t>0258361667</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>95886768</t>
+          <t>94459720</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>もどりち るかりん</t>
+          <t>えりっく さてぃん</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>天井の模様を眺める</t>
+          <t>メールの件名を考えすぎる</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>机の周りのケーブルを整理する</t>
+          <t>Wi-Fiが遅いときにまず自分を疑う</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5363649378</t>
+          <t>1498754221</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>83909838</t>
+          <t>83486148</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>らべるん みゃ</t>
+          <t>ががれで ぃみゅ</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>冷蔵庫の中を定期巡回する</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>USBメモリをなくさない一年にする</t>
+          <t>積読の本を一冊は読む</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5363649378</t>
+          <t>1498754221</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>91803905</t>
+          <t>97358186</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>らべるん みゃ</t>
+          <t>ががれで ぃみゅ</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>冷蔵庫の中を定期巡回する</t>
+          <t>YouTubeおすすめの深掘り</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>USBメモリをなくさない一年にする</t>
+          <t>積読の本を一冊は読む</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6904592348</t>
+          <t>2266827753</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>80722997</t>
+          <t>85148137</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>しどに すうぇり</t>
+          <t>ふくだん みらきゅ</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>スマホのバッテリー節約術研究</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ノートをちゃんと取る（たぶん）</t>
+          <t>プリンタの紙詰まりを自分で直せるようになる</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6904592348</t>
+          <t>2266827753</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>97898519</t>
+          <t>91999479</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>しどに すうぇり</t>
+          <t>ふくだん みらきゅ</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>新しいボールペンの試し書き</t>
+          <t>スマホのバッテリー節約術研究</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ノートをちゃんと取る（たぶん）</t>
+          <t>プリンタの紙詰まりを自分で直せるようになる</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6147116275</t>
+          <t>4509570099</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>80184530</t>
+          <t>87680200</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>おおさか なみりん</t>
+          <t>けいと うぃんり</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>イヤホンの絡まり解消</t>
+          <t>Google検索の予測変換観察</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>6147116275</t>
+          <t>4509570099</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>95912833</t>
+          <t>93239322</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>おおさか なみりん</t>
+          <t>けいと うぃんり</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>イヤホンの絡まり解消</t>
+          <t>Google検索の予測変換観察</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>研究テーマを説明できるようになる</t>
+          <t>ノートをちゃんと取る（たぶん）</t>
         </is>
       </c>
     </row>
